--- a/artfynd/A 51154-2025 artfynd.xlsx
+++ b/artfynd/A 51154-2025 artfynd.xlsx
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133929952</v>
+        <v>133929954</v>
       </c>
       <c r="B7" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>663867</v>
+        <v>663847</v>
       </c>
       <c r="R7" t="n">
-        <v>6666591</v>
+        <v>6666595</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133929954</v>
+        <v>133929952</v>
       </c>
       <c r="B8" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>663847</v>
+        <v>663867</v>
       </c>
       <c r="R8" t="n">
-        <v>6666595</v>
+        <v>6666591</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
         <v>133929955</v>
       </c>
       <c r="B9" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>133929947</v>
       </c>
       <c r="B10" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 51154-2025 artfynd.xlsx
+++ b/artfynd/A 51154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,69 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113031374</v>
+        <v>113031464</v>
       </c>
       <c r="B2" t="n">
-        <v>57176</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103001</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hemmingsby, Upl</t>
+          <t>Nipparbol, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663840</v>
+        <v>663931</v>
       </c>
       <c r="R2" t="n">
-        <v>6666579</v>
+        <v>6666564</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -796,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113031468</v>
+        <v>113031459</v>
       </c>
       <c r="B3" t="n">
-        <v>97335</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663930</v>
+        <v>663929</v>
       </c>
       <c r="R3" t="n">
-        <v>6666522</v>
+        <v>6666648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113031366</v>
+        <v>113031374</v>
       </c>
       <c r="B4" t="n">
-        <v>56910</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -957,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>663828</v>
+        <v>663840</v>
       </c>
       <c r="R4" t="n">
-        <v>6666513</v>
+        <v>6666579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,50 +985,64 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113031472</v>
+        <v>113031366</v>
       </c>
       <c r="B5" t="n">
-        <v>97336</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nipparbol, Upl</t>
+          <t>Hemmingsby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>663821</v>
+        <v>663828</v>
       </c>
       <c r="R5" t="n">
-        <v>6666489</v>
+        <v>6666513</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,12 +1069,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,15 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113031471</v>
+        <v>113031472</v>
       </c>
       <c r="B6" t="n">
-        <v>99570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663885</v>
+        <v>663821</v>
       </c>
       <c r="R6" t="n">
-        <v>6666488</v>
+        <v>6666489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133929954</v>
+        <v>113031468</v>
       </c>
       <c r="B7" t="n">
-        <v>101396</v>
+        <v>99141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,38 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Morkarla kyrka, 4,1 km S-ut, Upl</t>
+          <t>Nipparbol, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>663847</v>
+        <v>663930</v>
       </c>
       <c r="R7" t="n">
-        <v>6666595</v>
+        <v>6666522</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,12 +1263,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,33 +1277,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133929952</v>
+        <v>113031463</v>
       </c>
       <c r="B8" t="n">
-        <v>101396</v>
+        <v>99153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,38 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Morkarla kyrka, 4,1 km S-ut, Upl</t>
+          <t>Nipparbol, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>663867</v>
+        <v>663932</v>
       </c>
       <c r="R8" t="n">
-        <v>6666591</v>
+        <v>6666574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,12 +1360,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,33 +1374,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133929955</v>
+        <v>133929948</v>
       </c>
       <c r="B9" t="n">
-        <v>101396</v>
+        <v>108205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1446,21 +1403,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220083</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1470,14 +1427,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Morkarla kyrka, 4,1 km S-ut, Upl</t>
+          <t>Morkarla kyrka, 4,2 km S-ut, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>663766</v>
+        <v>663902</v>
       </c>
       <c r="R9" t="n">
-        <v>6666647</v>
+        <v>6666516</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133929947</v>
+        <v>113031471</v>
       </c>
       <c r="B10" t="n">
-        <v>101396</v>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,20 +1527,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Morkarla kyrka, 4,2 km S-ut, Upl</t>
+          <t>Nipparbol, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>663907</v>
+        <v>663885</v>
       </c>
       <c r="R10" t="n">
-        <v>6666509</v>
+        <v>6666488</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,12 +1563,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,22 +1577,985 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130772371</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Alunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>663967</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6666729</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Tufvesson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Helios Nordic Energy AB - NVI Alunda</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133929947</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Morkarla kyrka, 4,2 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>663907</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6666509</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Henry Åkerström</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Henry Åkerström, Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133929950</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Morkarla kyrka, 4,1 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>663927</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6666570</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133929952</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Morkarla kyrka, 4,1 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>663867</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6666591</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133929954</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Morkarla kyrka, 4,1 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>663847</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6666595</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133929955</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Morkarla kyrka, 4,1 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>663766</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6666647</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133929946</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Morkarla kyrka, 4,2 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>663826</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6666496</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133929949</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Morkarla kyrka, 4,2 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>663902</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6666516</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133929956</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Morkarla kyrka, 4,1 km S-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>663766</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6666647</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>

--- a/artfynd/A 51154-2025 artfynd.xlsx
+++ b/artfynd/A 51154-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113031464</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113031459</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113031374</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113031366</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113031472</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113031468</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113031463</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133929948</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113031471</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Helios Nordic Energy AB - NVI Alunda</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130772371</t>
         </is>
       </c>
     </row>
@@ -1818,6 +1873,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133929947</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1924,6 +1984,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133929950</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2030,6 +2095,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133929952</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2136,6 +2206,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133929954</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2242,6 +2317,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133929955</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2348,6 +2428,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133929946</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2454,6 +2539,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133929949</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,8 +2650,33 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133929956</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>